--- a/public/templates/teacher-upload-template.xlsx
+++ b/public/templates/teacher-upload-template.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -497,77 +497,220 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>John Ssali</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>jssali@kabalejunior.sch.ug</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>jssali@school.ug</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>P.5</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Primary Five</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>+256701234567</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Jane Okello</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Grace Nakamya</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gnakamya@school.ug</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>English, Science</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>P.5, P.6</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Primary Five, Primary Six</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>+256782255758</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Peter Kato</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>pkato@kabalejunior.sch.ug</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>History, Geography, RE</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>S.1, S.2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Peter Wasswa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pwasswa@school.ug</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Biology, Chemistry</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Senior One, Senior Two</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+256773456789</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sarah Nambi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>snambi@school.ug</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>History, Geography</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Senior Three, Senior Four</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+256764567890</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>David Okello</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dokello@school.ug</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Literacy, Numeracy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Baby Class, Middle Class</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+256775678901</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Esther Kyomuhangi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ekyomuhangi@school.ug</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>English, Social Studies</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Primary One, Primary Two</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+256786789012</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Robert Ssekitoleko</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rssekitoleko@school.ug</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Physics, Mathematics</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Senior Five, Senior Six</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+256797890123</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Martha Nansubuga</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mnansubuga@school.ug</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Motor Skills, Social/Emotional</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Top Class</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+256708901234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
